--- a/data/excel/ot_evidencias.xlsx
+++ b/data/excel/ot_evidencias.xlsx
@@ -44,6 +44,27 @@
   </x:si>
   <x:si>
     <x:t>Observaciones</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TipoEvidencia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EsFoto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EsObligatoria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StorageProvider</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LocalPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OfflineId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SyncStatus</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -422,9 +443,16 @@
     <x:col min="8" max="8" width="12.710625" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.424911" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.282054" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="6.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="15.424911" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="9.567768" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="8.567768" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="10.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:10">
+    <x:row r="1" spans="1:17">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -454,6 +482,27 @@
       </x:c>
       <x:c r="J1" s="1" t="s">
         <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M1" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N1" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O1" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P1" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q1" s="1" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
